--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/138.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/138.xlsx
@@ -426,13 +426,13 @@
         <v>-17.77905961929949</v>
       </c>
       <c r="E2">
-        <v>-10.20437030763782</v>
+        <v>-10.46505191388937</v>
       </c>
       <c r="F2">
-        <v>-3.648495499201165</v>
+        <v>-4.347722909006436</v>
       </c>
       <c r="G2">
-        <v>-6.261626573465564</v>
+        <v>-7.69840002696372</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.28871108645925</v>
       </c>
       <c r="E3">
-        <v>-9.884841181656604</v>
+        <v>-11.60416690814881</v>
       </c>
       <c r="F3">
-        <v>-3.604620191344487</v>
+        <v>-4.204915682233413</v>
       </c>
       <c r="G3">
-        <v>-6.089200119598163</v>
+        <v>-7.627696705881506</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.70552095987479</v>
       </c>
       <c r="E4">
-        <v>-11.73231366561786</v>
+        <v>-12.64560724653681</v>
       </c>
       <c r="F4">
-        <v>-4.031913635260945</v>
+        <v>-4.25398071186863</v>
       </c>
       <c r="G4">
-        <v>-4.983861932764142</v>
+        <v>-7.931670997297386</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.07896073962438</v>
       </c>
       <c r="E5">
-        <v>-10.65918306612419</v>
+        <v>-12.47631930270806</v>
       </c>
       <c r="F5">
-        <v>-3.349449896586127</v>
+        <v>-4.186405812617858</v>
       </c>
       <c r="G5">
-        <v>-5.282688325866456</v>
+        <v>-7.074709800092725</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.38872769476979</v>
       </c>
       <c r="E6">
-        <v>-11.94563196222318</v>
+        <v>-13.43921778790703</v>
       </c>
       <c r="F6">
-        <v>-3.92279114055536</v>
+        <v>-4.217036354071175</v>
       </c>
       <c r="G6">
-        <v>-4.217086617140307</v>
+        <v>-7.162608094705914</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.63320584054726</v>
       </c>
       <c r="E7">
-        <v>-14.12661749990135</v>
+        <v>-13.85490453096712</v>
       </c>
       <c r="F7">
-        <v>-4.01832178291581</v>
+        <v>-4.660329714372705</v>
       </c>
       <c r="G7">
-        <v>-4.195395922767003</v>
+        <v>-6.487746765434403</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.8126108041422</v>
       </c>
       <c r="E8">
-        <v>-14.17390835396345</v>
+        <v>-14.9791616020074</v>
       </c>
       <c r="F8">
-        <v>-4.374139545481713</v>
+        <v>-4.128218801143012</v>
       </c>
       <c r="G8">
-        <v>-2.601550325612586</v>
+        <v>-6.120077577842946</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.93218241154203</v>
       </c>
       <c r="E9">
-        <v>-13.91395130355314</v>
+        <v>-15.59730736100241</v>
       </c>
       <c r="F9">
-        <v>-4.376164075414154</v>
+        <v>-4.372533341087684</v>
       </c>
       <c r="G9">
-        <v>-2.865248519997693</v>
+        <v>-5.535759669070503</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.98083690631246</v>
       </c>
       <c r="E10">
-        <v>-14.59592137521226</v>
+        <v>-16.30983104679129</v>
       </c>
       <c r="F10">
-        <v>-4.456910016369439</v>
+        <v>-4.578790197445539</v>
       </c>
       <c r="G10">
-        <v>-3.112420471050758</v>
+        <v>-5.486945675093949</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.96943908503931</v>
       </c>
       <c r="E11">
-        <v>-15.88042755596197</v>
+        <v>-17.0002920072148</v>
       </c>
       <c r="F11">
-        <v>-4.507066834241546</v>
+        <v>-4.250642391235348</v>
       </c>
       <c r="G11">
-        <v>-2.662848386817731</v>
+        <v>-4.789029706686954</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.913482852669931</v>
       </c>
       <c r="E12">
-        <v>-17.59383003845214</v>
+        <v>-17.7350278580113</v>
       </c>
       <c r="F12">
-        <v>-4.167237390917077</v>
+        <v>-4.384016998392694</v>
       </c>
       <c r="G12">
-        <v>-1.32366650527175</v>
+        <v>-4.551147146417084</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.832616596541234</v>
       </c>
       <c r="E13">
-        <v>-17.42582365276757</v>
+        <v>-18.36315437371922</v>
       </c>
       <c r="F13">
-        <v>-4.73235874514833</v>
+        <v>-4.458671953835194</v>
       </c>
       <c r="G13">
-        <v>-1.014113944622198</v>
+        <v>-3.693179543368485</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.771962631442959</v>
       </c>
       <c r="E14">
-        <v>-18.47721304855042</v>
+        <v>-18.90046234320332</v>
       </c>
       <c r="F14">
-        <v>-4.673649862209722</v>
+        <v>-4.61381605633811</v>
       </c>
       <c r="G14">
-        <v>-1.234112937888926</v>
+        <v>-3.52413646704222</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.781652032862586</v>
       </c>
       <c r="E15">
-        <v>-18.94722336580652</v>
+        <v>-20.25020119203351</v>
       </c>
       <c r="F15">
-        <v>-4.411575125149028</v>
+        <v>-4.066412652485336</v>
       </c>
       <c r="G15">
-        <v>0.6627137870195902</v>
+        <v>-3.185110119456536</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.907184391659752</v>
       </c>
       <c r="E16">
-        <v>-19.95719533831522</v>
+        <v>-20.67371766665287</v>
       </c>
       <c r="F16">
-        <v>-4.399214226764453</v>
+        <v>-4.112201489042481</v>
       </c>
       <c r="G16">
-        <v>1.033676967422623</v>
+        <v>-2.663056951186705</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.20226976145341</v>
       </c>
       <c r="E17">
-        <v>-20.31643918134371</v>
+        <v>-21.69618822742274</v>
       </c>
       <c r="F17">
-        <v>-4.60762566673699</v>
+        <v>-3.933977413962764</v>
       </c>
       <c r="G17">
-        <v>2.052580120771812</v>
+        <v>-2.11408573713706</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.708425221652584</v>
       </c>
       <c r="E18">
-        <v>-21.71444703462166</v>
+        <v>-22.29032401722909</v>
       </c>
       <c r="F18">
-        <v>-4.325893771207864</v>
+        <v>-3.79812350316884</v>
       </c>
       <c r="G18">
-        <v>1.870950350305238</v>
+        <v>-2.226078182185065</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.441334598222441</v>
       </c>
       <c r="E19">
-        <v>-22.69945805840008</v>
+        <v>-22.82072153537748</v>
       </c>
       <c r="F19">
-        <v>-4.037841432395378</v>
+        <v>-3.440638237021102</v>
       </c>
       <c r="G19">
-        <v>2.563533029848467</v>
+        <v>-1.87829213110247</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.400677762583232</v>
       </c>
       <c r="E20">
-        <v>-21.66504138319798</v>
+        <v>-23.76861265771502</v>
       </c>
       <c r="F20">
-        <v>-3.946647293388583</v>
+        <v>-3.270049224292988</v>
       </c>
       <c r="G20">
-        <v>2.066517517492144</v>
+        <v>-2.022158508602578</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.564907575118053</v>
       </c>
       <c r="E21">
-        <v>-23.26274588326618</v>
+        <v>-24.05305063861081</v>
       </c>
       <c r="F21">
-        <v>-3.407272426403741</v>
+        <v>-3.174595620100999</v>
       </c>
       <c r="G21">
-        <v>1.800730368871757</v>
+        <v>-2.401583443403988</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.89098943607671</v>
       </c>
       <c r="E22">
-        <v>-24.83186212692396</v>
+        <v>-24.8119277843422</v>
       </c>
       <c r="F22">
-        <v>-2.972512907085851</v>
+        <v>-2.966020991750111</v>
       </c>
       <c r="G22">
-        <v>2.662342882559094</v>
+        <v>-2.338749289068621</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.326989559542281</v>
       </c>
       <c r="E23">
-        <v>-23.91369137949876</v>
+        <v>-24.88907939601087</v>
       </c>
       <c r="F23">
-        <v>-3.061149047552801</v>
+        <v>-2.648117605210342</v>
       </c>
       <c r="G23">
-        <v>1.85567880373258</v>
+        <v>-1.874551214643094</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.814680188007064</v>
       </c>
       <c r="E24">
-        <v>-24.36617650234518</v>
+        <v>-26.17256214163485</v>
       </c>
       <c r="F24">
-        <v>-2.514729744174552</v>
+        <v>-2.71755550275001</v>
       </c>
       <c r="G24">
-        <v>0.3092766347014589</v>
+        <v>-2.506832307188498</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.293691502705482</v>
       </c>
       <c r="E25">
-        <v>-23.66877339126792</v>
+        <v>-25.20735866316598</v>
       </c>
       <c r="F25">
-        <v>-3.074952133585649</v>
+        <v>-2.601043142444052</v>
       </c>
       <c r="G25">
-        <v>0.0537124507063411</v>
+        <v>-2.624955882575233</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.712966192724948</v>
       </c>
       <c r="E26">
-        <v>-25.86685844679904</v>
+        <v>-25.56287557208616</v>
       </c>
       <c r="F26">
-        <v>-3.243855418649066</v>
+        <v>-2.393733431117239</v>
       </c>
       <c r="G26">
-        <v>0.4409866889813631</v>
+        <v>-2.098976407295827</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.036525664135324</v>
       </c>
       <c r="E27">
-        <v>-25.04055685156745</v>
+        <v>-25.57865730400289</v>
       </c>
       <c r="F27">
-        <v>-3.082047928758029</v>
+        <v>-2.322657851222236</v>
       </c>
       <c r="G27">
-        <v>0.6155716185403685</v>
+        <v>-3.04341214928465</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.245505576444473</v>
       </c>
       <c r="E28">
-        <v>-24.63512257366072</v>
+        <v>-26.09006693063712</v>
       </c>
       <c r="F28">
-        <v>-2.405621331714815</v>
+        <v>-2.196817245593352</v>
       </c>
       <c r="G28">
-        <v>0.9128718501490781</v>
+        <v>-3.208797072790021</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.337987974584267</v>
       </c>
       <c r="E29">
-        <v>-25.29571371952964</v>
+        <v>-25.88296170037032</v>
       </c>
       <c r="F29">
-        <v>-2.893332580521857</v>
+        <v>-2.245347978253764</v>
       </c>
       <c r="G29">
-        <v>0.2577877199291742</v>
+        <v>-2.632020586756038</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.327617550646235</v>
       </c>
       <c r="E30">
-        <v>-24.45257072946351</v>
+        <v>-25.24831871056536</v>
       </c>
       <c r="F30">
-        <v>-2.678690989312866</v>
+        <v>-2.168562461851264</v>
       </c>
       <c r="G30">
-        <v>0.2773398018841098</v>
+        <v>-3.166415468796271</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.237906952079087</v>
       </c>
       <c r="E31">
-        <v>-24.22256953461394</v>
+        <v>-24.46664522667935</v>
       </c>
       <c r="F31">
-        <v>-2.5835993816759</v>
+        <v>-2.265527836553363</v>
       </c>
       <c r="G31">
-        <v>-0.4446968013220147</v>
+        <v>-3.179770209501691</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.093754792290431</v>
       </c>
       <c r="E32">
-        <v>-23.46462978300213</v>
+        <v>-24.58098013842502</v>
       </c>
       <c r="F32">
-        <v>-2.21273598197295</v>
+        <v>-2.151971919507995</v>
       </c>
       <c r="G32">
-        <v>0.07464834069669209</v>
+        <v>-2.908437897103025</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.91968759552821</v>
       </c>
       <c r="E33">
-        <v>-23.75691560935321</v>
+        <v>-24.24903393671476</v>
       </c>
       <c r="F33">
-        <v>-2.578576161745324</v>
+        <v>-2.475116386605277</v>
       </c>
       <c r="G33">
-        <v>0.1349962753320665</v>
+        <v>-3.203400883561009</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.736485099566988</v>
       </c>
       <c r="E34">
-        <v>-22.95248201510466</v>
+        <v>-24.03102414103749</v>
       </c>
       <c r="F34">
-        <v>-2.692129593688483</v>
+        <v>-2.200535786864519</v>
       </c>
       <c r="G34">
-        <v>-0.4022026387799297</v>
+        <v>-2.898085821201724</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.556589832036671</v>
       </c>
       <c r="E35">
-        <v>-23.16957705903237</v>
+        <v>-23.51963715677331</v>
       </c>
       <c r="F35">
-        <v>-2.394575052398483</v>
+        <v>-2.162916309633782</v>
       </c>
       <c r="G35">
-        <v>-0.3510116731061793</v>
+        <v>-2.955659518675189</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.388287919429948</v>
       </c>
       <c r="E36">
-        <v>-22.34530422015621</v>
+        <v>-23.73053724825853</v>
       </c>
       <c r="F36">
-        <v>-2.305280359846308</v>
+        <v>-2.227292053974943</v>
       </c>
       <c r="G36">
-        <v>0.2287078879122161</v>
+        <v>-3.132634662113548</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.236242745071449</v>
       </c>
       <c r="E37">
-        <v>-22.98892264544438</v>
+        <v>-23.42455731650826</v>
       </c>
       <c r="F37">
-        <v>-2.467593153853052</v>
+        <v>-1.988635263391391</v>
       </c>
       <c r="G37">
-        <v>0.4782237052070854</v>
+        <v>-2.222893437376287</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.09942339735066</v>
       </c>
       <c r="E38">
-        <v>-20.81466642014161</v>
+        <v>-23.0604906486616</v>
       </c>
       <c r="F38">
-        <v>-2.165659862471854</v>
+        <v>-2.05776252315501</v>
       </c>
       <c r="G38">
-        <v>0.8161145356727991</v>
+        <v>-2.370073670961205</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.976984758880599</v>
       </c>
       <c r="E39">
-        <v>-20.88738918423079</v>
+        <v>-21.90509126187058</v>
       </c>
       <c r="F39">
-        <v>-2.198782961440195</v>
+        <v>-2.29100676112867</v>
       </c>
       <c r="G39">
-        <v>0.4727281996118952</v>
+        <v>-2.175178544518771</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.86860815253864</v>
       </c>
       <c r="E40">
-        <v>-19.81276871678859</v>
+        <v>-22.5841087684767</v>
       </c>
       <c r="F40">
-        <v>-1.979003007231639</v>
+        <v>-2.342148507842706</v>
       </c>
       <c r="G40">
-        <v>0.7751663978975538</v>
+        <v>-2.418050096916323</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.771855696395282</v>
       </c>
       <c r="E41">
-        <v>-20.47310173963907</v>
+        <v>-21.37465751593013</v>
       </c>
       <c r="F41">
-        <v>-2.26234027878739</v>
+        <v>-2.222869400411396</v>
       </c>
       <c r="G41">
-        <v>0.7738554218640025</v>
+        <v>-1.930919873540264</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.687695131598857</v>
       </c>
       <c r="E42">
-        <v>-19.77766851475513</v>
+        <v>-21.04041084942398</v>
       </c>
       <c r="F42">
-        <v>-1.951313998425662</v>
+        <v>-2.000774987679418</v>
       </c>
       <c r="G42">
-        <v>0.6187828477134615</v>
+        <v>-1.923957796271177</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.618761253494931</v>
       </c>
       <c r="E43">
-        <v>-19.64943571627994</v>
+        <v>-20.1192467806797</v>
       </c>
       <c r="F43">
-        <v>-2.633601294843684</v>
+        <v>-2.276463943005122</v>
       </c>
       <c r="G43">
-        <v>0.3668304689016885</v>
+        <v>-2.260862084166188</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.56301625442369</v>
       </c>
       <c r="E44">
-        <v>-18.96930873354193</v>
+        <v>-20.84723067673077</v>
       </c>
       <c r="F44">
-        <v>-2.016079903813542</v>
+        <v>-2.214419224535439</v>
       </c>
       <c r="G44">
-        <v>0.5925997430433656</v>
+        <v>-2.132777077251786</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.518798991774317</v>
       </c>
       <c r="E45">
-        <v>-19.28326783649372</v>
+        <v>-19.4603719264597</v>
       </c>
       <c r="F45">
-        <v>-1.873462373175759</v>
+        <v>-2.245185618242815</v>
       </c>
       <c r="G45">
-        <v>-0.3287946019921304</v>
+        <v>-2.531651467096414</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.485831360332504</v>
       </c>
       <c r="E46">
-        <v>-18.98586483451398</v>
+        <v>-19.17916274753138</v>
       </c>
       <c r="F46">
-        <v>-2.014917704347414</v>
+        <v>-2.564059851378665</v>
       </c>
       <c r="G46">
-        <v>-0.04252510812027231</v>
+        <v>-1.688644219339781</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.459799804992238</v>
       </c>
       <c r="E47">
-        <v>-17.82238665009327</v>
+        <v>-18.67808257010865</v>
       </c>
       <c r="F47">
-        <v>-2.073577713609258</v>
+        <v>-2.291677738724937</v>
       </c>
       <c r="G47">
-        <v>0.6691461770023941</v>
+        <v>-2.260458197610397</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.438703171859929</v>
       </c>
       <c r="E48">
-        <v>-16.73389546676557</v>
+        <v>-18.20192258515013</v>
       </c>
       <c r="F48">
-        <v>-2.042207440065241</v>
+        <v>-2.298414850811906</v>
       </c>
       <c r="G48">
-        <v>0.3802745943366688</v>
+        <v>-2.390013086744236</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.422753067173144</v>
       </c>
       <c r="E49">
-        <v>-16.45984127676938</v>
+        <v>-17.0678930672013</v>
       </c>
       <c r="F49">
-        <v>-2.88167496606226</v>
+        <v>-2.269025203727982</v>
       </c>
       <c r="G49">
-        <v>0.4213485328424064</v>
+        <v>-2.252446677405361</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.408608208992169</v>
       </c>
       <c r="E50">
-        <v>-16.34092354932796</v>
+        <v>-17.21659909666518</v>
       </c>
       <c r="F50">
-        <v>-2.340287994656018</v>
+        <v>-2.24035209444748</v>
       </c>
       <c r="G50">
-        <v>0.1531115805229585</v>
+        <v>-2.259531244859401</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.396452220644062</v>
       </c>
       <c r="E51">
-        <v>-14.82185147192894</v>
+        <v>-16.64774124876964</v>
       </c>
       <c r="F51">
-        <v>-2.294335969720521</v>
+        <v>-2.328200457514368</v>
       </c>
       <c r="G51">
-        <v>-0.9462047239751282</v>
+        <v>-2.460948146014199</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.389086580732474</v>
       </c>
       <c r="E52">
-        <v>-15.81069358471785</v>
+        <v>-16.25778076654713</v>
       </c>
       <c r="F52">
-        <v>-2.167597413827002</v>
+        <v>-2.398137032230521</v>
       </c>
       <c r="G52">
-        <v>0.05295102523230872</v>
+        <v>-2.369424804035508</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.384879706007654</v>
       </c>
       <c r="E53">
-        <v>-13.76684835388797</v>
+        <v>-16.44726570445008</v>
       </c>
       <c r="F53">
-        <v>-2.275812846226521</v>
+        <v>-2.343927841023919</v>
       </c>
       <c r="G53">
-        <v>0.2435523741103081</v>
+        <v>-2.649510198840007</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.383459002581589</v>
       </c>
       <c r="E54">
-        <v>-14.84631428851838</v>
+        <v>-14.70567347126216</v>
       </c>
       <c r="F54">
-        <v>-2.063262882709599</v>
+        <v>-2.406583066269465</v>
       </c>
       <c r="G54">
-        <v>-0.1779793894050922</v>
+        <v>-2.702945714389384</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.38473403001494</v>
       </c>
       <c r="E55">
-        <v>-13.77509470505594</v>
+        <v>-14.86613089077594</v>
       </c>
       <c r="F55">
-        <v>-1.844620276945086</v>
+        <v>-2.482924577744065</v>
       </c>
       <c r="G55">
-        <v>-0.9541169278139864</v>
+        <v>-2.747777122082194</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.384078374693921</v>
       </c>
       <c r="E56">
-        <v>-13.0361428449583</v>
+        <v>-14.61198840099147</v>
       </c>
       <c r="F56">
-        <v>-1.91617548156631</v>
+        <v>-2.250926204344216</v>
       </c>
       <c r="G56">
-        <v>-1.767991374825033</v>
+        <v>-3.337656747360613</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.379024074071082</v>
       </c>
       <c r="E57">
-        <v>-13.40186240581776</v>
+        <v>-13.88662196291684</v>
       </c>
       <c r="F57">
-        <v>-2.032350696339329</v>
+        <v>-2.185586240346196</v>
       </c>
       <c r="G57">
-        <v>-0.6571477507592038</v>
+        <v>-3.222936412788248</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.368454373175886</v>
       </c>
       <c r="E58">
-        <v>-12.90275211458836</v>
+        <v>-14.96896800701613</v>
       </c>
       <c r="F58">
-        <v>-2.216930834500727</v>
+        <v>-2.070486246462011</v>
       </c>
       <c r="G58">
-        <v>-1.457051695594526</v>
+        <v>-3.252039418623981</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.347546220936096</v>
       </c>
       <c r="E59">
-        <v>-11.8678871204595</v>
+        <v>-13.9074348294561</v>
       </c>
       <c r="F59">
-        <v>-2.102695656185064</v>
+        <v>-2.346084909740809</v>
       </c>
       <c r="G59">
-        <v>-1.938166657725729</v>
+        <v>-3.604913778200436</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.314361951739027</v>
       </c>
       <c r="E60">
-        <v>-10.79693018848951</v>
+        <v>-14.01053006871472</v>
       </c>
       <c r="F60">
-        <v>-1.742426247196517</v>
+        <v>-2.225595557534009</v>
       </c>
       <c r="G60">
-        <v>-2.004576201243509</v>
+        <v>-3.953491049666917</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.267675409577216</v>
       </c>
       <c r="E61">
-        <v>-10.96741817793028</v>
+        <v>-13.78991640048304</v>
       </c>
       <c r="F61">
-        <v>-2.070611329939833</v>
+        <v>-2.146595815063826</v>
       </c>
       <c r="G61">
-        <v>-1.389814515691928</v>
+        <v>-3.874004851269016</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.2027180133309</v>
       </c>
       <c r="E62">
-        <v>-10.35253292022078</v>
+        <v>-12.74070520069788</v>
       </c>
       <c r="F62">
-        <v>-1.840130525621913</v>
+        <v>-2.237315299548817</v>
       </c>
       <c r="G62">
-        <v>-1.830040929867593</v>
+        <v>-3.951180288880506</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.118651509272788</v>
       </c>
       <c r="E63">
-        <v>-10.31932562032254</v>
+        <v>-12.6649710013936</v>
       </c>
       <c r="F63">
-        <v>-2.261638651597219</v>
+        <v>-2.450318380035071</v>
       </c>
       <c r="G63">
-        <v>-1.667354100976728</v>
+        <v>-4.16433638451756</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.016658372529808</v>
       </c>
       <c r="E64">
-        <v>-10.08068862554033</v>
+        <v>-12.65641218551911</v>
       </c>
       <c r="F64">
-        <v>-2.120217283489079</v>
+        <v>-2.104124589954893</v>
       </c>
       <c r="G64">
-        <v>-2.740328394618834</v>
+        <v>-4.571209052385067</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.89637157094221</v>
       </c>
       <c r="E65">
-        <v>-10.38071814244452</v>
+        <v>-12.06182354831199</v>
       </c>
       <c r="F65">
-        <v>-2.035784279223933</v>
+        <v>-2.473771946310533</v>
       </c>
       <c r="G65">
-        <v>-2.294507158481801</v>
+        <v>-4.219771469572656</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.762037671371447</v>
       </c>
       <c r="E66">
-        <v>-8.628262100112202</v>
+        <v>-11.68262724880571</v>
       </c>
       <c r="F66">
-        <v>-2.334134881588023</v>
+        <v>-2.446198080573546</v>
       </c>
       <c r="G66">
-        <v>-2.269668135300649</v>
+        <v>-3.861163245122183</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.619485199604362</v>
       </c>
       <c r="E67">
-        <v>-8.663575140424015</v>
+        <v>-12.11501047553208</v>
       </c>
       <c r="F67">
-        <v>-1.930392751300558</v>
+        <v>-2.359691672699193</v>
       </c>
       <c r="G67">
-        <v>-2.866437005846291</v>
+        <v>-4.494222315869316</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.471917558663756</v>
       </c>
       <c r="E68">
-        <v>-9.304897629390291</v>
+        <v>-12.18643809605506</v>
       </c>
       <c r="F68">
-        <v>-1.630641379658335</v>
+        <v>-2.540396708150294</v>
       </c>
       <c r="G68">
-        <v>-2.767832406959099</v>
+        <v>-4.335332682711996</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.324956058688058</v>
       </c>
       <c r="E69">
-        <v>-8.419476805988561</v>
+        <v>-12.26949483782975</v>
       </c>
       <c r="F69">
-        <v>-1.809263899458798</v>
+        <v>-2.416318868354568</v>
       </c>
       <c r="G69">
-        <v>-2.495828053815961</v>
+        <v>-4.81021719813829</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.184614263669623</v>
       </c>
       <c r="E70">
-        <v>-8.622891329939105</v>
+        <v>-11.7041737281342</v>
       </c>
       <c r="F70">
-        <v>-1.871830489392244</v>
+        <v>-2.662318307596534</v>
       </c>
       <c r="G70">
-        <v>-3.097231688116582</v>
+        <v>-4.404996492494879</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.054595773332934</v>
       </c>
       <c r="E71">
-        <v>-9.388094753859212</v>
+        <v>-11.5990859603122</v>
       </c>
       <c r="F71">
-        <v>-2.04197052698804</v>
+        <v>-2.53462547245499</v>
       </c>
       <c r="G71">
-        <v>-2.698747942645588</v>
+        <v>-4.274107453508714</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.94018311618746</v>
       </c>
       <c r="E72">
-        <v>-9.738779781013204</v>
+        <v>-11.34356228595539</v>
       </c>
       <c r="F72">
-        <v>-2.136121109255427</v>
+        <v>-2.658220374054885</v>
       </c>
       <c r="G72">
-        <v>-2.750448732332386</v>
+        <v>-4.905544356941604</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.847331097908269</v>
       </c>
       <c r="E73">
-        <v>-9.135858751631973</v>
+        <v>-12.25161642244746</v>
       </c>
       <c r="F73">
-        <v>-2.128314574851444</v>
+        <v>-2.948150621769517</v>
       </c>
       <c r="G73">
-        <v>-2.651625637439602</v>
+        <v>-4.658964993540068</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.77991789425178</v>
       </c>
       <c r="E74">
-        <v>-8.684931423844189</v>
+        <v>-12.13567843090309</v>
       </c>
       <c r="F74">
-        <v>-2.128930880199127</v>
+        <v>-2.756360373734153</v>
       </c>
       <c r="G74">
-        <v>-2.531426349999744</v>
+        <v>-4.841978572042058</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.742376340325904</v>
       </c>
       <c r="E75">
-        <v>-9.268266803142247</v>
+        <v>-12.04375493702138</v>
       </c>
       <c r="F75">
-        <v>-2.257187833541977</v>
+        <v>-2.580579154125293</v>
       </c>
       <c r="G75">
-        <v>-3.090484796307547</v>
+        <v>-4.369494202131735</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.740329574174462</v>
       </c>
       <c r="E76">
-        <v>-9.463724798261314</v>
+        <v>-13.15853391196361</v>
       </c>
       <c r="F76">
-        <v>-2.573813049179226</v>
+        <v>-2.720146635985968</v>
       </c>
       <c r="G76">
-        <v>-2.532412892570446</v>
+        <v>-4.017040281838767</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.777681317655784</v>
       </c>
       <c r="E77">
-        <v>-9.361177504357618</v>
+        <v>-12.61030326317301</v>
       </c>
       <c r="F77">
-        <v>-2.418717820353075</v>
+        <v>-2.832947081959982</v>
       </c>
       <c r="G77">
-        <v>-2.53670998068042</v>
+        <v>-4.739199375229845</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.855434284191184</v>
       </c>
       <c r="E78">
-        <v>-11.10701291769073</v>
+        <v>-13.31727503982848</v>
       </c>
       <c r="F78">
-        <v>-2.763844673218447</v>
+        <v>-2.995048642279011</v>
       </c>
       <c r="G78">
-        <v>-2.204688747455835</v>
+        <v>-3.79031757058178</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.973145625324245</v>
       </c>
       <c r="E79">
-        <v>-11.2926758235312</v>
+        <v>-13.68143227715529</v>
       </c>
       <c r="F79">
-        <v>-2.900166611594953</v>
+        <v>-2.97348623878414</v>
       </c>
       <c r="G79">
-        <v>-2.330972817596873</v>
+        <v>-4.027014955548592</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.128638860280116</v>
       </c>
       <c r="E80">
-        <v>-11.44764473254769</v>
+        <v>-14.4671813876482</v>
       </c>
       <c r="F80">
-        <v>-2.977956109289646</v>
+        <v>-3.037005451230806</v>
       </c>
       <c r="G80">
-        <v>-2.602695774369173</v>
+        <v>-4.124371478767478</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.316460350802075</v>
       </c>
       <c r="E81">
-        <v>-12.03848832175047</v>
+        <v>-14.83492970486309</v>
       </c>
       <c r="F81">
-        <v>-2.835622708671024</v>
+        <v>-3.449777614576189</v>
       </c>
       <c r="G81">
-        <v>-2.041290151274026</v>
+        <v>-3.760496176364025</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.531483178600608</v>
       </c>
       <c r="E82">
-        <v>-11.59525487130171</v>
+        <v>-15.96911319092818</v>
       </c>
       <c r="F82">
-        <v>-2.819004830203463</v>
+        <v>-3.10295012343287</v>
       </c>
       <c r="G82">
-        <v>-2.114787572791386</v>
+        <v>-3.747114951294291</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.771491668402612</v>
       </c>
       <c r="E83">
-        <v>-13.07314500607497</v>
+        <v>-16.31930914288935</v>
       </c>
       <c r="F83">
-        <v>-3.193701085879166</v>
+        <v>-3.155719612093407</v>
       </c>
       <c r="G83">
-        <v>-1.870869888003424</v>
+        <v>-3.39871975983247</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.033327115883925</v>
       </c>
       <c r="E84">
-        <v>-12.77870815457025</v>
+        <v>-16.95723527634987</v>
       </c>
       <c r="F84">
-        <v>-3.227245823855533</v>
+        <v>-3.283686636845277</v>
       </c>
       <c r="G84">
-        <v>-2.179803376637133</v>
+        <v>-3.498297659108208</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.316688709617793</v>
       </c>
       <c r="E85">
-        <v>-15.58534766114816</v>
+        <v>-17.96370673845064</v>
       </c>
       <c r="F85">
-        <v>-3.21730872849155</v>
+        <v>-3.217751076684645</v>
       </c>
       <c r="G85">
-        <v>-2.027793057110418</v>
+        <v>-3.607522488085382</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.62858163646979</v>
       </c>
       <c r="E86">
-        <v>-16.64982434681318</v>
+        <v>-19.15183340689509</v>
       </c>
       <c r="F86">
-        <v>-3.593309662826662</v>
+        <v>-3.778353686733627</v>
       </c>
       <c r="G86">
-        <v>-1.088770057078303</v>
+        <v>-3.341632712553277</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.973807676378303</v>
       </c>
       <c r="E87">
-        <v>-16.96992406051936</v>
+        <v>-20.33719317772086</v>
       </c>
       <c r="F87">
-        <v>-3.709243822685467</v>
+        <v>-3.620507449762778</v>
       </c>
       <c r="G87">
-        <v>-1.500469500342067</v>
+        <v>-3.288501767193514</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.357820976003014</v>
       </c>
       <c r="E88">
-        <v>-18.47765231052916</v>
+        <v>-21.65564027115806</v>
       </c>
       <c r="F88">
-        <v>-3.949779350538567</v>
+        <v>-3.695006672133552</v>
       </c>
       <c r="G88">
-        <v>-1.663795264522012</v>
+        <v>-3.818420791664653</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.793484213812102</v>
       </c>
       <c r="E89">
-        <v>-19.90467409677426</v>
+        <v>-22.95216955039812</v>
       </c>
       <c r="F89">
-        <v>-3.797529563741032</v>
+        <v>-4.134591431572749</v>
       </c>
       <c r="G89">
-        <v>-2.064857924968098</v>
+        <v>-3.18858950281831</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.286475309018526</v>
       </c>
       <c r="E90">
-        <v>-21.9787831193974</v>
+        <v>-24.13694514807691</v>
       </c>
       <c r="F90">
-        <v>-4.222077798084613</v>
+        <v>-4.284734680064965</v>
       </c>
       <c r="G90">
-        <v>-2.367269638889443</v>
+        <v>-3.519918832025188</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.838307145872955</v>
       </c>
       <c r="E91">
-        <v>-24.11012299652948</v>
+        <v>-26.57618955841251</v>
       </c>
       <c r="F91">
-        <v>-4.013307675026665</v>
+        <v>-3.956424513843825</v>
       </c>
       <c r="G91">
-        <v>-1.27079709300959</v>
+        <v>-2.957870963095422</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.455567565523916</v>
       </c>
       <c r="E92">
-        <v>-24.49845775658324</v>
+        <v>-27.61994394701843</v>
       </c>
       <c r="F92">
-        <v>-4.252191438278583</v>
+        <v>-4.34219687006236</v>
       </c>
       <c r="G92">
-        <v>-1.890362380138653</v>
+        <v>-3.31640966608957</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.131287910073944</v>
       </c>
       <c r="E93">
-        <v>-26.9018955229402</v>
+        <v>-29.19897754875301</v>
       </c>
       <c r="F93">
-        <v>-4.839562740949032</v>
+        <v>-4.371897154922334</v>
       </c>
       <c r="G93">
-        <v>-2.048536935459491</v>
+        <v>-3.987225508712091</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.850710259729068</v>
       </c>
       <c r="E94">
-        <v>-28.98482148445627</v>
+        <v>-32.08849718661929</v>
       </c>
       <c r="F94">
-        <v>-4.371067130784729</v>
+        <v>-4.643144404234227</v>
       </c>
       <c r="G94">
-        <v>-1.863143074714765</v>
+        <v>-3.593303694994213</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.60392436911725</v>
       </c>
       <c r="E95">
-        <v>-30.40532226813032</v>
+        <v>-34.23663770231983</v>
       </c>
       <c r="F95">
-        <v>-4.75748312847524</v>
+        <v>-4.567571617709425</v>
       </c>
       <c r="G95">
-        <v>-1.284542478088644</v>
+        <v>-3.591807328410462</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.36896405814161</v>
       </c>
       <c r="E96">
-        <v>-34.46157832746584</v>
+        <v>-36.2786489011766</v>
       </c>
       <c r="F96">
-        <v>-5.176624608780747</v>
+        <v>-4.96581007497269</v>
       </c>
       <c r="G96">
-        <v>-2.056843094217522</v>
+        <v>-3.619973449858581</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.11200466455512</v>
       </c>
       <c r="E97">
-        <v>-36.27025763884038</v>
+        <v>-37.75691037081849</v>
       </c>
       <c r="F97">
-        <v>-5.203266561189585</v>
+        <v>-5.036261065845983</v>
       </c>
       <c r="G97">
-        <v>-2.014438316404998</v>
+        <v>-4.382067654089886</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.81984230945203</v>
       </c>
       <c r="E98">
-        <v>-38.59577848142137</v>
+        <v>-40.77026565889853</v>
       </c>
       <c r="F98">
-        <v>-5.698102598028107</v>
+        <v>-5.250684796428037</v>
       </c>
       <c r="G98">
-        <v>-2.415726093947755</v>
+        <v>-4.42575030248057</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.45525730554731</v>
       </c>
       <c r="E99">
-        <v>-40.02922617228335</v>
+        <v>-42.5124782930255</v>
       </c>
       <c r="F99">
-        <v>-6.267687195825643</v>
+        <v>-5.084854754429007</v>
       </c>
       <c r="G99">
-        <v>-2.941520178676962</v>
+        <v>-5.382358920417293</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.01496730756389</v>
       </c>
       <c r="E100">
-        <v>-42.94241840802474</v>
+        <v>-45.65038925868651</v>
       </c>
       <c r="F100">
-        <v>-6.01908171273447</v>
+        <v>-5.443229687167351</v>
       </c>
       <c r="G100">
-        <v>-2.813630493949376</v>
+        <v>-5.145926379093624</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.46856885791548</v>
       </c>
       <c r="E101">
-        <v>-45.43116130350118</v>
+        <v>-47.81794787093194</v>
       </c>
       <c r="F101">
-        <v>-6.463540171788037</v>
+        <v>-5.631779361922963</v>
       </c>
       <c r="G101">
-        <v>-3.546101936695284</v>
+        <v>-4.96938491712091</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.85816311707474</v>
       </c>
       <c r="E102">
-        <v>-49.4013412610174</v>
+        <v>-50.13605560156236</v>
       </c>
       <c r="F102">
-        <v>-6.514489323080922</v>
+        <v>-5.707528590704562</v>
       </c>
       <c r="G102">
-        <v>-3.480040000459127</v>
+        <v>-5.503855941708546</v>
       </c>
     </row>
   </sheetData>
